--- a/exports/trend_1d/DMART_full_report.xlsx
+++ b/exports/trend_1d/DMART_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.45</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43031</v>
+        <v>43032</v>
       </c>
       <c r="H2" t="n">
-        <v>1126.4</v>
+        <v>1092.9</v>
       </c>
       <c r="I2" t="n">
         <v>1101.128931015059</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K2" t="n">
-        <v>78.19</v>
+        <v>72.89</v>
       </c>
       <c r="L2" t="n">
         <v>0.61</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>17.39</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43103</v>
+        <v>43104</v>
       </c>
       <c r="H3" t="n">
-        <v>1184.55</v>
+        <v>1203.1</v>
       </c>
       <c r="I3" t="n">
         <v>1201.224680403835</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.390000000000001</v>
+        <v>-10.08</v>
       </c>
       <c r="L3" t="n">
-        <v>10.2</v>
+        <v>11.17</v>
       </c>
       <c r="M3" t="n">
         <v>1.47</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.66</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43117</v>
+        <v>43118</v>
       </c>
       <c r="H4" t="n">
-        <v>1167.35</v>
+        <v>1135.45</v>
       </c>
       <c r="I4" t="n">
         <v>1149.588419560117</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.97</v>
+        <v>-5.62</v>
       </c>
       <c r="L4" t="n">
-        <v>4.25</v>
+        <v>6.36</v>
       </c>
       <c r="M4" t="n">
         <v>0.34</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.11</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43151</v>
+        <v>43152</v>
       </c>
       <c r="H5" t="n">
-        <v>1186.8</v>
+        <v>1237.8</v>
       </c>
       <c r="I5" t="n">
         <v>1236.379522085896</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.52</v>
+        <v>-9.01</v>
       </c>
       <c r="L5" t="n">
         <v>11.3</v>
@@ -726,7 +785,7 @@
         <v>3.51</v>
       </c>
       <c r="N5" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>-2.73</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.39</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43238</v>
+        <v>43241</v>
       </c>
       <c r="H6" t="n">
-        <v>1417.2</v>
+        <v>1345.45</v>
       </c>
       <c r="I6" t="n">
         <v>1412.434306387446</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K6" t="n">
-        <v>14.49</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>4.48</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>13.81</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43248</v>
+        <v>43249</v>
       </c>
       <c r="H7" t="n">
-        <v>1528.9</v>
+        <v>1544.05</v>
       </c>
       <c r="I7" t="n">
         <v>1529.461315669468</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>-13.63</v>
+        <v>-14.76</v>
       </c>
       <c r="L7" t="n">
-        <v>13.72</v>
+        <v>15.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.28</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>12.95</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43278</v>
+        <v>43279</v>
       </c>
       <c r="H8" t="n">
-        <v>1452.5</v>
+        <v>1435.45</v>
       </c>
       <c r="I8" t="n">
         <v>1444.631539884381</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.93</v>
+        <v>-7.03</v>
       </c>
       <c r="L8" t="n">
-        <v>7.64</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>2.13</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>9.02</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43286</v>
+        <v>43287</v>
       </c>
       <c r="H9" t="n">
-        <v>1546.45</v>
+        <v>1568.25</v>
       </c>
       <c r="I9" t="n">
         <v>1564.882934354062</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.73</v>
+        <v>-9.25</v>
       </c>
       <c r="L9" t="n">
-        <v>8.75</v>
+        <v>10.07</v>
       </c>
       <c r="M9" t="n">
         <v>0.71</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>8.27</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43350</v>
+        <v>43353</v>
       </c>
       <c r="H10" t="n">
-        <v>1561.2</v>
+        <v>1526.4</v>
       </c>
       <c r="I10" t="n">
         <v>1541.938604703823</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.45</v>
+        <v>-2.67</v>
       </c>
       <c r="L10" t="n">
-        <v>3.97</v>
+        <v>8.56</v>
       </c>
       <c r="M10" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="O10" t="n">
         <v>1.41</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.62</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43404</v>
+        <v>43405</v>
       </c>
       <c r="H11" t="n">
-        <v>1337.95</v>
+        <v>1366.1</v>
       </c>
       <c r="I11" t="n">
         <v>1358.0363638136</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K11" t="n">
-        <v>12.35</v>
+        <v>10.5</v>
       </c>
       <c r="L11" t="n">
         <v>3.1</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>14.97</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43476</v>
+        <v>43479</v>
       </c>
       <c r="H12" t="n">
-        <v>1571.65</v>
+        <v>1397.4</v>
       </c>
       <c r="I12" t="n">
         <v>1539.563828171061</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K12" t="n">
-        <v>15.05</v>
+        <v>2.29</v>
       </c>
       <c r="L12" t="n">
         <v>1.46</v>
       </c>
       <c r="M12" t="n">
-        <v>2.18</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>6.21</v>
+        <v>11.09</v>
       </c>
       <c r="O12" t="n">
         <v>2.1</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>14.68</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43501</v>
+        <v>43502</v>
       </c>
       <c r="H13" t="n">
-        <v>1471.7</v>
+        <v>1512.65</v>
       </c>
       <c r="I13" t="n">
         <v>1496.904897687361</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.32</v>
+        <v>-8.25</v>
       </c>
       <c r="L13" t="n">
-        <v>6.79</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>0.43</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>11.11</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43571</v>
+        <v>43573</v>
       </c>
       <c r="H14" t="n">
-        <v>1410.65</v>
+        <v>1358.5</v>
       </c>
       <c r="I14" t="n">
         <v>1399.808024080547</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.74</v>
+        <v>-10.19</v>
       </c>
       <c r="L14" t="n">
-        <v>7.78</v>
+        <v>10.55</v>
       </c>
       <c r="M14" t="n">
         <v>1.9</v>
       </c>
       <c r="N14" t="n">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="O14" t="n">
         <v>2.78</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.81</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43641</v>
+        <v>43642</v>
       </c>
       <c r="H15" t="n">
-        <v>1330.65</v>
+        <v>1387.45</v>
       </c>
       <c r="I15" t="n">
         <v>1354.817017735229</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K15" t="n">
-        <v>2.05</v>
+        <v>-2.13</v>
       </c>
       <c r="L15" t="n">
         <v>4.82</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.07</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43784</v>
+        <v>43787</v>
       </c>
       <c r="H16" t="n">
-        <v>1870.85</v>
+        <v>1829.45</v>
       </c>
       <c r="I16" t="n">
         <v>1852.432636897515</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K16" t="n">
-        <v>34.84</v>
+        <v>31.86</v>
       </c>
       <c r="L16" t="n">
         <v>7.29</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43815</v>
+        <v>43816</v>
       </c>
       <c r="H17" t="n">
-        <v>1770.4</v>
+        <v>1883.95</v>
       </c>
       <c r="I17" t="n">
         <v>1857.791842932604</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>3.23</v>
+        <v>-2.98</v>
       </c>
       <c r="L17" t="n">
-        <v>2.27</v>
+        <v>4.5</v>
       </c>
       <c r="M17" t="n">
         <v>0.93</v>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>6.41</v>
       </c>
       <c r="O17" t="n">
         <v>-2.21</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.08</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43893</v>
+        <v>43894</v>
       </c>
       <c r="H18" t="n">
-        <v>2233.05</v>
+        <v>2198.45</v>
       </c>
       <c r="I18" t="n">
         <v>2205.9600165305</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K18" t="n">
-        <v>18.53</v>
+        <v>16.69</v>
       </c>
       <c r="L18" t="n">
         <v>5.94</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>15.16</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43928</v>
+        <v>43929</v>
       </c>
       <c r="H19" t="n">
-        <v>2170.25</v>
+        <v>2278.75</v>
       </c>
       <c r="I19" t="n">
         <v>2203.094711386955</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>1.28</v>
+        <v>-3.65</v>
       </c>
       <c r="L19" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
         <v>4.7</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>18.13</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44025</v>
+        <v>44026</v>
       </c>
       <c r="H20" t="n">
-        <v>2233.95</v>
+        <v>2154.85</v>
       </c>
       <c r="I20" t="n">
         <v>2166.811652883197</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.97</v>
+        <v>-5.44</v>
       </c>
       <c r="L20" t="n">
         <v>7.63</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>11.34</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44060</v>
+        <v>44061</v>
       </c>
       <c r="H21" t="n">
-        <v>2189.75</v>
+        <v>2259.45</v>
       </c>
       <c r="I21" t="n">
         <v>2224.1385988096</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.62</v>
+        <v>-4.85</v>
       </c>
       <c r="L21" t="n">
-        <v>3.02</v>
+        <v>5.17</v>
       </c>
       <c r="M21" t="n">
         <v>1.67</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>9.56</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44085</v>
+        <v>44088</v>
       </c>
       <c r="H22" t="n">
-        <v>2239.35</v>
+        <v>2162.7</v>
       </c>
       <c r="I22" t="n">
         <v>2200.034549943687</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.89</v>
+        <v>-4.28</v>
       </c>
       <c r="L22" t="n">
-        <v>3.96</v>
+        <v>4.84</v>
       </c>
       <c r="M22" t="n">
         <v>1.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.94</v>
+        <v>3.42</v>
       </c>
       <c r="O22" t="n">
         <v>3.18</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>12.16</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44130</v>
+        <v>44131</v>
       </c>
       <c r="H23" t="n">
-        <v>2144.25</v>
+        <v>2176.2</v>
       </c>
       <c r="I23" t="n">
         <v>2166.580003932656</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K23" t="n">
-        <v>0.85</v>
+        <v>-0.62</v>
       </c>
       <c r="L23" t="n">
         <v>4.45</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.41</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H24" t="n">
-        <v>2855.6</v>
+        <v>2796</v>
       </c>
       <c r="I24" t="n">
         <v>2827.422565293291</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K24" t="n">
-        <v>31.22</v>
+        <v>28.48</v>
       </c>
       <c r="L24" t="n">
         <v>2.96</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>14.17</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H25" t="n">
-        <v>2898.7</v>
+        <v>3056.3</v>
       </c>
       <c r="I25" t="n">
         <v>2998.89699036219</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.67</v>
+        <v>-9.31</v>
       </c>
       <c r="L25" t="n">
-        <v>6.87</v>
+        <v>10.16</v>
       </c>
       <c r="M25" t="n">
         <v>1.35</v>
       </c>
       <c r="N25" t="n">
-        <v>3.89</v>
+        <v>5.44</v>
       </c>
       <c r="O25" t="n">
         <v>-2.09</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>10.68</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44488</v>
+        <v>44489</v>
       </c>
       <c r="H26" t="n">
-        <v>4754.55</v>
+        <v>4596.4</v>
       </c>
       <c r="I26" t="n">
         <v>4616.633954643517</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K26" t="n">
-        <v>55.57</v>
+        <v>50.39</v>
       </c>
       <c r="L26" t="n">
         <v>4.76</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>22.63</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44708</v>
+        <v>44711</v>
       </c>
       <c r="H27" t="n">
-        <v>3613.85</v>
+        <v>3796.4</v>
       </c>
       <c r="I27" t="n">
         <v>3690.422296826957</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K27" t="n">
-        <v>21.38</v>
+        <v>17.4</v>
       </c>
       <c r="L27" t="n">
         <v>12.7</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>150</v>
+        <v>151</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>9</v>
+      </c>
+      <c r="U27" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>13.83</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44741</v>
+        <v>44742</v>
       </c>
       <c r="H28" t="n">
-        <v>3445.25</v>
+        <v>3406.1</v>
       </c>
       <c r="I28" t="n">
         <v>3406.897098114972</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K28" t="n">
-        <v>-9.25</v>
+        <v>-10.28</v>
       </c>
       <c r="L28" t="n">
-        <v>11.13</v>
+        <v>11.23</v>
       </c>
       <c r="M28" t="n">
         <v>1.48</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>10.7</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44747</v>
+        <v>44748</v>
       </c>
       <c r="H29" t="n">
-        <v>3639.05</v>
+        <v>3792</v>
       </c>
       <c r="I29" t="n">
         <v>3707.361440483936</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.84</v>
+        <v>-11.33</v>
       </c>
       <c r="L29" t="n">
-        <v>7.39</v>
+        <v>12.45</v>
       </c>
       <c r="M29" t="n">
         <v>4.17</v>
       </c>
       <c r="N29" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="O29" t="n">
         <v>-1.14</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.61</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44832</v>
+        <v>44833</v>
       </c>
       <c r="H30" t="n">
-        <v>4318.15</v>
+        <v>4240.55</v>
       </c>
       <c r="I30" t="n">
         <v>4260.108585168011</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K30" t="n">
-        <v>13.88</v>
+        <v>11.83</v>
       </c>
       <c r="L30" t="n">
         <v>3.74</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.36</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44908</v>
+        <v>44909</v>
       </c>
       <c r="H31" t="n">
-        <v>4108.95</v>
+        <v>4201.1</v>
       </c>
       <c r="I31" t="n">
         <v>4138.093602295839</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K31" t="n">
-        <v>3.1</v>
+        <v>0.93</v>
       </c>
       <c r="L31" t="n">
         <v>8.48</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>7.03</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H32" t="n">
-        <v>3993.2</v>
+        <v>3921.55</v>
       </c>
       <c r="I32" t="n">
         <v>3947.230668397207</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.95</v>
+        <v>-6.65</v>
       </c>
       <c r="L32" t="n">
-        <v>5.83</v>
+        <v>7.04</v>
       </c>
       <c r="M32" t="n">
         <v>0.99</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.98</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44923</v>
+        <v>44924</v>
       </c>
       <c r="H33" t="n">
-        <v>4017.75</v>
+        <v>4178.3</v>
       </c>
       <c r="I33" t="n">
         <v>4175.019144331321</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.45</v>
+        <v>-6.55</v>
       </c>
       <c r="L33" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="M33" t="n">
         <v>0.58</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>10.45</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44939</v>
+        <v>44942</v>
       </c>
       <c r="H34" t="n">
-        <v>3863.7</v>
+        <v>3678.35</v>
       </c>
       <c r="I34" t="n">
         <v>3745.597959213798</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.53</v>
+        <v>-11.97</v>
       </c>
       <c r="L34" t="n">
-        <v>8.220000000000001</v>
+        <v>12.76</v>
       </c>
       <c r="M34" t="n">
-        <v>0.36</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
-        <v>3.37</v>
+        <v>4.8</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.08</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H35" t="n">
-        <v>3401.05</v>
+        <v>3553.75</v>
       </c>
       <c r="I35" t="n">
         <v>3511.472797193399</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K35" t="n">
-        <v>7.54</v>
+        <v>3.39</v>
       </c>
       <c r="L35" t="n">
         <v>1.89</v>
@@ -2436,7 +2855,7 @@
         <v>1.59</v>
       </c>
       <c r="N35" t="n">
-        <v>2.32</v>
+        <v>4.49</v>
       </c>
       <c r="O35" t="n">
         <v>-4.8</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.16</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45061</v>
+        <v>45062</v>
       </c>
       <c r="H36" t="n">
-        <v>3523.4</v>
+        <v>3479.25</v>
       </c>
       <c r="I36" t="n">
         <v>3498.231430973468</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.85</v>
+        <v>-2.1</v>
       </c>
       <c r="L36" t="n">
         <v>3.96</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>7.8</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45085</v>
+        <v>45086</v>
       </c>
       <c r="H37" t="n">
-        <v>3546.8</v>
+        <v>3632.1</v>
       </c>
       <c r="I37" t="n">
         <v>3630.47905609854</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.94</v>
+        <v>-4.39</v>
       </c>
       <c r="L37" t="n">
-        <v>2.69</v>
+        <v>4.85</v>
       </c>
       <c r="M37" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
         <v>-1.25</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>5.65</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45099</v>
+        <v>45100</v>
       </c>
       <c r="H38" t="n">
-        <v>3812.15</v>
+        <v>3744.05</v>
       </c>
       <c r="I38" t="n">
         <v>3756.246333808728</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>4.96</v>
+        <v>3.08</v>
       </c>
       <c r="L38" t="n">
         <v>1.75</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.36</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45167</v>
+        <v>45168</v>
       </c>
       <c r="H39" t="n">
-        <v>3664.35</v>
+        <v>3736.3</v>
       </c>
       <c r="I39" t="n">
         <v>3683.200817999402</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K39" t="n">
-        <v>2.13</v>
+        <v>0.21</v>
       </c>
       <c r="L39" t="n">
         <v>6.52</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.65</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45226</v>
+        <v>45229</v>
       </c>
       <c r="H40" t="n">
-        <v>3665.45</v>
+        <v>3646.65</v>
       </c>
       <c r="I40" t="n">
         <v>3650.143145255051</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.9</v>
+        <v>-2.4</v>
       </c>
       <c r="L40" t="n">
         <v>3.22</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>7.33</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45254</v>
+        <v>45258</v>
       </c>
       <c r="H41" t="n">
-        <v>3842.9</v>
+        <v>3912.15</v>
       </c>
       <c r="I41" t="n">
         <v>3853.996864480241</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.38</v>
+        <v>-7.28</v>
       </c>
       <c r="L41" t="n">
-        <v>6.23</v>
+        <v>7.88</v>
       </c>
       <c r="M41" t="n">
         <v>0.58</v>
       </c>
       <c r="N41" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="O41" t="n">
         <v>-0.51</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>6.13</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45295</v>
+        <v>45296</v>
       </c>
       <c r="H42" t="n">
-        <v>3897.85</v>
+        <v>3863.5</v>
       </c>
       <c r="I42" t="n">
         <v>3889.200519599868</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.37</v>
+        <v>-1.24</v>
       </c>
       <c r="L42" t="n">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="M42" t="n">
         <v>0.73</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.77</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="H43" t="n">
-        <v>3850</v>
+        <v>3918.9</v>
       </c>
       <c r="I43" t="n">
         <v>3898.559755900226</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K43" t="n">
-        <v>0.35</v>
+        <v>-1.43</v>
       </c>
       <c r="L43" t="n">
         <v>2.19</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.53</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H44" t="n">
-        <v>4476.85</v>
+        <v>4444.95</v>
       </c>
       <c r="I44" t="n">
         <v>4446.886529382157</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K44" t="n">
-        <v>14.24</v>
+        <v>13.42</v>
       </c>
       <c r="L44" t="n">
         <v>3.11</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>8.81</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45447</v>
+        <v>45448</v>
       </c>
       <c r="H45" t="n">
-        <v>4548.75</v>
+        <v>4862.25</v>
       </c>
       <c r="I45" t="n">
         <v>4744.140761701029</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.34</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>3.26</v>
+        <v>10.24</v>
       </c>
       <c r="M45" t="n">
         <v>2.11</v>
       </c>
       <c r="N45" t="n">
-        <v>4.58</v>
+        <v>6.89</v>
       </c>
       <c r="O45" t="n">
         <v>-0.71</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>12.76</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H46" t="n">
-        <v>4954.35</v>
+        <v>4942.6</v>
       </c>
       <c r="I46" t="n">
         <v>4947.053268032965</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K46" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="L46" t="n">
         <v>6.17</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>9.35</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="H47" t="n">
-        <v>3611.1</v>
+        <v>4025.2</v>
       </c>
       <c r="I47" t="n">
         <v>3723.89449050522</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K47" t="n">
-        <v>26.94</v>
+        <v>18.56</v>
       </c>
       <c r="L47" t="n">
         <v>1.46</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>6.34</v>
       </c>
       <c r="N47" t="n">
-        <v>4.12</v>
+        <v>11.47</v>
       </c>
       <c r="O47" t="n">
         <v>-0.24</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>11.02</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H48" t="n">
-        <v>3686.25</v>
+        <v>3507.45</v>
       </c>
       <c r="I48" t="n">
         <v>3581.429308609097</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>-8.42</v>
+        <v>-12.86</v>
       </c>
       <c r="L48" t="n">
-        <v>8.91</v>
+        <v>13.79</v>
       </c>
       <c r="M48" t="n">
-        <v>0.02</v>
+        <v>5.03</v>
       </c>
       <c r="N48" t="n">
-        <v>3.34</v>
+        <v>4.85</v>
       </c>
       <c r="O48" t="n">
         <v>11.47</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>13.49</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H49" t="n">
-        <v>3664.65</v>
+        <v>4023.75</v>
       </c>
       <c r="I49" t="n">
         <v>3833.408370716911</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.48</v>
+        <v>-14.72</v>
       </c>
       <c r="L49" t="n">
-        <v>5.6</v>
+        <v>16.46</v>
       </c>
       <c r="M49" t="n">
         <v>0.68</v>
       </c>
       <c r="N49" t="n">
-        <v>2.64</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O49" t="n">
         <v>-4.85</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>13.68</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="H50" t="n">
-        <v>3570.9</v>
+        <v>3530.75</v>
       </c>
       <c r="I50" t="n">
         <v>3558.456897747372</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>-11.25</v>
+        <v>-12.25</v>
       </c>
       <c r="L50" t="n">
-        <v>11.64</v>
+        <v>12.6</v>
       </c>
       <c r="M50" t="n">
         <v>3.08</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>8.83</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45728</v>
+        <v>45729</v>
       </c>
       <c r="H51" t="n">
-        <v>3674.2</v>
+        <v>3797.1</v>
       </c>
       <c r="I51" t="n">
         <v>3721.610923212432</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.06</v>
+        <v>-7.54</v>
       </c>
       <c r="L51" t="n">
-        <v>4.37</v>
+        <v>9.81</v>
       </c>
       <c r="M51" t="n">
         <v>0.88</v>
       </c>
       <c r="N51" t="n">
-        <v>1.94</v>
+        <v>3.34</v>
       </c>
       <c r="O51" t="n">
         <v>-1.12</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45777</v>
+        <v>45779</v>
       </c>
       <c r="H52" t="n">
-        <v>4199.9</v>
+        <v>4059.2</v>
       </c>
       <c r="I52" t="n">
         <v>4121.047254449665</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K52" t="n">
-        <v>10.61</v>
+        <v>6.9</v>
       </c>
       <c r="L52" t="n">
         <v>3.35</v>
@@ -3405,7 +4028,7 @@
         <v>6.9</v>
       </c>
       <c r="N52" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="O52" t="n">
         <v>3.34</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>12.23</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45827</v>
+        <v>45828</v>
       </c>
       <c r="H53" t="n">
-        <v>4203.1</v>
+        <v>4300.3</v>
       </c>
       <c r="I53" t="n">
         <v>4276.496745674889</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.55</v>
+        <v>-5.94</v>
       </c>
       <c r="L53" t="n">
-        <v>4.8</v>
+        <v>6.54</v>
       </c>
       <c r="M53" t="n">
         <v>1.95</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>9.09</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H54" t="n">
-        <v>4169</v>
+        <v>4064.2</v>
       </c>
       <c r="I54" t="n">
         <v>4140.152000417157</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.05</v>
+        <v>-5.49</v>
       </c>
       <c r="L54" t="n">
-        <v>3.49</v>
+        <v>6.03</v>
       </c>
       <c r="M54" t="n">
         <v>0.97</v>
       </c>
       <c r="N54" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="O54" t="n">
         <v>2.31</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>8.69</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45867</v>
+        <v>45868</v>
       </c>
       <c r="H55" t="n">
-        <v>3999</v>
+        <v>4281.4</v>
       </c>
       <c r="I55" t="n">
         <v>4212.32189084079</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K55" t="n">
-        <v>1.6</v>
+        <v>-5.34</v>
       </c>
       <c r="L55" t="n">
-        <v>2.97</v>
+        <v>6.39</v>
       </c>
       <c r="M55" t="n">
         <v>0.67</v>
       </c>
       <c r="N55" t="n">
-        <v>1.47</v>
+        <v>7.06</v>
       </c>
       <c r="O55" t="n">
         <v>-2.51</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.19</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H56" t="n">
-        <v>4576.2</v>
+        <v>4517.8</v>
       </c>
       <c r="I56" t="n">
         <v>4524.931624366854</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K56" t="n">
-        <v>6.89</v>
+        <v>5.52</v>
       </c>
       <c r="L56" t="n">
         <v>6.6</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="H57" t="n">
-        <v>3824.3</v>
+        <v>3934.9</v>
       </c>
       <c r="I57" t="n">
         <v>3848.096722529076</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K57" t="n">
-        <v>15.35</v>
+        <v>12.9</v>
       </c>
       <c r="L57" t="n">
         <v>2.47</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>6</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>9.08</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="H58" t="n">
-        <v>3770.8</v>
+        <v>3655.6</v>
       </c>
       <c r="I58" t="n">
         <v>3718.850565175591</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.17</v>
+        <v>-7.1</v>
       </c>
       <c r="L58" t="n">
-        <v>5.97</v>
+        <v>7.75</v>
       </c>
       <c r="M58" t="n">
         <v>3.84</v>
       </c>
       <c r="N58" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="O58" t="n">
         <v>2.89</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>9.99</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="H59" t="n">
-        <v>3956.8</v>
+        <v>4271.1</v>
       </c>
       <c r="I59" t="n">
         <v>4020.791813704915</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.24</v>
+        <v>-16.84</v>
       </c>
       <c r="L59" t="n">
-        <v>9.83</v>
+        <v>17.49</v>
       </c>
       <c r="M59" t="n">
-        <v>2.04</v>
+        <v>2.99</v>
       </c>
       <c r="N59" t="n">
-        <v>4.11</v>
+        <v>7.94</v>
       </c>
       <c r="O59" t="n">
         <v>-3.06</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>12.05</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="H60" t="n">
-        <v>4236</v>
+        <v>4144.2</v>
       </c>
       <c r="I60" t="n">
         <v>4232.633998917599</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.82</v>
+        <v>-2.97</v>
       </c>
       <c r="L60" t="n">
         <v>4.8</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>8.1</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="H61" t="n">
-        <v>4286.9</v>
+        <v>4330.6</v>
       </c>
       <c r="I61" t="n">
         <v>4308.214298139719</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.44</v>
+        <v>-4.5</v>
       </c>
       <c r="L61" t="n">
-        <v>4.96</v>
+        <v>5.02</v>
       </c>
       <c r="M61" t="n">
         <v>1.45</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>6.92</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="H62" t="n">
-        <v>4187</v>
+        <v>3994.4</v>
       </c>
       <c r="I62" t="n">
         <v>4061.401230800884</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.32</v>
+        <v>-7.76</v>
       </c>
       <c r="L62" t="n">
-        <v>3.57</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>0.45</v>
+        <v>2.32</v>
       </c>
       <c r="N62" t="n">
-        <v>3.27</v>
+        <v>4.6</v>
       </c>
       <c r="O62" t="n">
         <v>1.02</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,14 @@
       <c r="Q63" t="n">
         <v>81</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8109,7 +8872,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.8</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="6">
@@ -8119,7 +8882,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -8129,7 +8892,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
@@ -8139,7 +8902,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -8149,7 +8912,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -8159,7 +8922,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -8169,7 +8932,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -8179,7 +8942,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -8189,7 +8952,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="14">
@@ -8199,7 +8962,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.87</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="15">
@@ -8209,7 +8972,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.28</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="16">
@@ -8219,7 +8982,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.35</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="17">
@@ -8229,7 +8992,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>78.19</v>
+        <v>72.89</v>
       </c>
     </row>
     <row r="18">
@@ -8239,7 +9002,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.6</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="19">
@@ -8249,7 +9012,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.43</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="20">
@@ -8259,7 +9022,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.76</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="21">
@@ -8269,7 +9032,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.72</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="22">
@@ -8279,7 +9042,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -8289,7 +9052,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -8299,7 +9062,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.94</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="25">
@@ -8309,7 +9072,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.9</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -8319,7 +9082,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.03</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="27">
@@ -8329,7 +9092,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.23</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="28">
@@ -8339,7 +9102,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
